--- a/Result/profitability/2634.xlsx
+++ b/Result/profitability/2634.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23625</v>
+        <v>0.33125</v>
       </c>
       <c r="N2" t="n">
-        <v>7.61125</v>
+        <v>8.936250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.215</v>
+        <v>0.27</v>
       </c>
       <c r="N3" t="n">
-        <v>7.147500000000001</v>
+        <v>8.466249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.3375</v>
       </c>
       <c r="N4" t="n">
-        <v>7.703749999999999</v>
+        <v>9.274999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1020,16 +1020,16 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23125</v>
+        <v>0.38875</v>
       </c>
       <c r="N5" t="n">
-        <v>7.828749999999999</v>
+        <v>9.237499999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0.33375</v>
+        <v>0.43625</v>
       </c>
       <c r="N6" t="n">
-        <v>8.23</v>
+        <v>9.9475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.37625</v>
+        <v>0.43375</v>
       </c>
       <c r="N7" t="n">
-        <v>8.98875</v>
+        <v>10.27125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8433,6 +8433,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9196</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1746</v>
+      </c>
+      <c r="F64" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>15.22%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>-155</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1245</v>
+      </c>
+      <c r="K64" t="n">
+        <v>965</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="N64" t="n">
+        <v>8.967500000000001</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.642857142857143</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.434615384615384</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.459844559585492</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
